--- a/tests/fixtures/20_sales_report/pattern-from-draft.xlsx
+++ b/tests/fixtures/20_sales_report/pattern-from-draft.xlsx
@@ -26,12 +26,37 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE8D0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D0E8FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D0FFD0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0E0E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8D0FF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +71,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -415,345 +445,412 @@
   </sheetPr>
   <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>config:</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>read.direction</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>LR</t>
         </is>
       </c>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>config:</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>currency.sign</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>€</t>
         </is>
       </c>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>lbl:</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>col_product</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Produkt</t>
         </is>
       </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>lbl:</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>col_q1</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Summe aus Qrtl 1</t>
         </is>
       </c>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>lbl:</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>col_q2</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Summe aus Qrtl 2</t>
         </is>
       </c>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>lbl:</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>col_q3</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Summe aus Qrtl 3</t>
         </is>
       </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>lbl:</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>col_q4</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Summe aus Qrtl 4</t>
         </is>
       </c>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>var:</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>line.product</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>.*</t>
         </is>
       </c>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>var:</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>line.q1</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>.*</t>
         </is>
       </c>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>var:</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>line.q2</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>.*</t>
         </is>
       </c>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>var:</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>line.q3</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>.*</t>
         </is>
       </c>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>var:</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>line.q4</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>.*</t>
         </is>
       </c>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="3" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>START:</t>
         </is>
       </c>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>table:*</t>
         </is>
       </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr">
+      <c r="A15" s="2" t="n"/>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>HEADER:1</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>col_product</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>col_q1</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>col_q2</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>col_q3</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>col_q4</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="inlineStr">
+      <c r="A16" s="3" t="n"/>
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>DATA:*</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>line.product</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>line.q1</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>line.q2</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>line.q3</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>line.q4</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>END:</t>
         </is>
       </c>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tests/fixtures/20_sales_report/pattern-from-draft.xlsx
+++ b/tests/fixtures/20_sales_report/pattern-from-draft.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Pattern" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,37 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE8D0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D0E8FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D0FFD0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E0E0E0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8D0FF"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -71,13 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -443,414 +413,403 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>config:</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>read.direction</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>LR</t>
         </is>
       </c>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>config:</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>currency.sign</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>€</t>
         </is>
       </c>
-      <c r="D2" s="1" t="n"/>
-      <c r="E2" s="1" t="n"/>
-      <c r="F2" s="1" t="n"/>
-      <c r="G2" s="1" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>lbl:</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>col_product</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Produkt</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>lbl:</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>col_customer</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Kunde</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>lbl:</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>col_q1</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Summe aus Qrtl 1</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Qrtl 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>lbl:</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>col_q2</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Summe aus Qrtl 2</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Qrtl 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>lbl:</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>col_q3</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Summe aus Qrtl 3</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Qrtl 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>lbl:</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>col_q4</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Summe aus Qrtl 4</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Qrtl 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>var:</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>line.product</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>.*</t>
         </is>
       </c>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="3" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>var:</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>line.customer</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>[A-Z]+</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>line.q1</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>.*</t>
         </is>
       </c>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>var:</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>line.q2</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>.*</t>
         </is>
       </c>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="3" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>var:</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>line.q3</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>.*</t>
         </is>
       </c>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>var:</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>line.q4</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>.*</t>
         </is>
       </c>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="3" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>START:</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>table:*</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n"/>
-      <c r="B15" s="2" t="inlineStr">
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
         <is>
           <t>HEADER:1</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>col_product</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>col_customer</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t>col_q1</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>col_q2</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>col_q3</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>col_q4</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="n"/>
-      <c r="B16" s="3" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
         <is>
           <t>DATA:*</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>line.product</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>line.customer</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>line.q1</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>line.q2</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>line.q3</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>line.q4</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>END:</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="4" t="n"/>
-      <c r="G17" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
